--- a/data/trans_camb/IP1019-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1019-Edad-trans_camb.xlsx
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,0</t>
+          <t>-1,43; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,0</t>
+          <t>-1,44; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,0</t>
+          <t>-1,67; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,0</t>
+          <t>-1,6; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,0</t>
+          <t>-0,97; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,0</t>
+          <t>-0,97; 0,0</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,0</t>
+          <t>-0,5; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
